--- a/docs/test-data/grades-import.xlsx
+++ b/docs/test-data/grades-import.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,36 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>student_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>subject_assignment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>subject_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>grading_period</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>letter_grade</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>remarks</t>
         </is>
@@ -460,23 +461,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_ASSIGNMENT_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_GRADING_PERIOD_UUID</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+          <t>ENG-8</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Term 3</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>88</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>B+</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Satisfactory</t>
         </is>
@@ -490,23 +496,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_ASSIGNMENT_UUID</t>
+          <t>Grade 8 - Bonifacio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>REPLACE_WITH_GRADING_PERIOD_UUID</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+          <t>ENG-8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Term 3</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>92.5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>A-</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Very satisfactory</t>
         </is>
